--- a/artfynd/A 26518-2026 artfynd.xlsx
+++ b/artfynd/A 26518-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136578385</v>
       </c>
       <c r="B2" t="n">
-        <v>91573</v>
+        <v>91575</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26518-2026 artfynd.xlsx
+++ b/artfynd/A 26518-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136578385</v>
       </c>
       <c r="B2" t="n">
-        <v>91575</v>
+        <v>91577</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26518-2026 artfynd.xlsx
+++ b/artfynd/A 26518-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136578385</v>
       </c>
       <c r="B2" t="n">
-        <v>91577</v>
+        <v>91579</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26518-2026 artfynd.xlsx
+++ b/artfynd/A 26518-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136578385</v>
       </c>
       <c r="B2" t="n">
-        <v>91579</v>
+        <v>91581</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26518-2026 artfynd.xlsx
+++ b/artfynd/A 26518-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136578385</v>
       </c>
       <c r="B2" t="n">
-        <v>91581</v>
+        <v>91583</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26518-2026 artfynd.xlsx
+++ b/artfynd/A 26518-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136578385</v>
       </c>
       <c r="B2" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26518-2026 artfynd.xlsx
+++ b/artfynd/A 26518-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136578385</v>
       </c>
       <c r="B2" t="n">
-        <v>91584</v>
+        <v>91590</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26518-2026 artfynd.xlsx
+++ b/artfynd/A 26518-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136578385</v>
       </c>
       <c r="B2" t="n">
-        <v>91590</v>
+        <v>91594</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26518-2026 artfynd.xlsx
+++ b/artfynd/A 26518-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136578385</v>
       </c>
       <c r="B2" t="n">
-        <v>91594</v>
+        <v>91596</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
